--- a/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>c</t>
   </si>
@@ -94,6 +94,10 @@
   </si>
   <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -221,7 +225,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -256,7 +260,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -471,7 +475,9 @@
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="10" width="8.88671875"/>
+    <col min="4" max="8" width="8.88671875"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -559,7 +565,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>24</v>
@@ -636,6 +642,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>c</t>
   </si>
@@ -33,9 +33,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>形状</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>销毁前触发</t>
   </si>
   <si>
-    <t>模型</t>
-  </si>
-  <si>
     <t>Shape</t>
   </si>
   <si>
@@ -87,9 +81,6 @@
     <t>DestroyAction</t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
     <t>string[]</t>
   </si>
   <si>
@@ -97,6 +88,85 @@
   </si>
   <si>
     <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标个数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetNum</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>nt</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算次数限制</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ickLimit</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ick1</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tick2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹自身生命周期tick，1档(0.1s)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹自身生命周期tick，2档(1s)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +200,14 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -158,13 +236,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -469,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:L9"/>
+  <dimension ref="B3:O9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -478,74 +557,96 @@
     <col min="4" max="8" width="8.88671875"/>
     <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.88671875"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
@@ -553,31 +654,40 @@
         <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>4</v>
+      <c r="M5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -590,8 +700,11 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
     </row>
-    <row r="7" spans="2:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -604,8 +717,11 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
     </row>
-    <row r="8" spans="2:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
@@ -621,8 +737,11 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
     </row>
-    <row r="9" spans="2:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,6 +757,9 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -19,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -45,9 +39,6 @@
     <t>创建时触发</t>
   </si>
   <si>
-    <t>结算间隔</t>
-  </si>
-  <si>
     <t>结算技能编号</t>
   </si>
   <si>
@@ -70,9 +61,6 @@
   </si>
   <si>
     <t>Interval</t>
-  </si>
-  <si>
-    <t>TickCastId</t>
   </si>
   <si>
     <t>TickAction</t>
@@ -132,8 +120,72 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>ickLimit</t>
+      <t>ick1</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tick2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹自身生命周期tick，1档(0.1s)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹自身生命周期tick，2档(1s)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"5"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TickCastId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -149,24 +201,8 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>ick1</t>
+      <t>ickLimit</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tick2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>子弹自身生命周期tick，1档(0.1s)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>子弹自身生命周期tick，2档(1s)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -174,7 +210,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +222,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -193,11 +230,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -208,6 +247,14 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -236,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -244,6 +291,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -548,218 +596,410 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:O9"/>
+  <dimension ref="C2:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="8" width="8.88671875"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="4" t="s">
+      <c r="P4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="I5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="P5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-    </row>
-    <row r="7" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="1">
+        <v>100</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-    </row>
-    <row r="8" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1">
         <v>1</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-    </row>
-    <row r="9" spans="2:15" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1004</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1">
+        <v>500</v>
+      </c>
+      <c r="I8" s="1">
+        <v>100</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7</v>
+      </c>
+      <c r="N8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="3:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="4:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="4:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="4:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="4:16" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
